--- a/04_Structural_QC/data/structural_wells_100_linear.xlsx
+++ b/04_Structural_QC/data/structural_wells_100_linear.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\projects\My_project\ML_Geophysics\structural_qc_project\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{202B775C-4E19-4A48-B727-99C639C74E5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="27634" windowHeight="16629" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="wells" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -31,371 +37,371 @@
     <t>Z_map</t>
   </si>
   <si>
+    <t>well_category</t>
+  </si>
+  <si>
+    <t>reservoir_flag</t>
+  </si>
+  <si>
+    <t>fluid_type</t>
+  </si>
+  <si>
+    <t>T_well</t>
+  </si>
+  <si>
+    <t>T_map</t>
+  </si>
+  <si>
+    <t>W-001</t>
+  </si>
+  <si>
+    <t>W-002</t>
+  </si>
+  <si>
+    <t>W-003</t>
+  </si>
+  <si>
+    <t>W-004</t>
+  </si>
+  <si>
+    <t>W-005</t>
+  </si>
+  <si>
+    <t>W-006</t>
+  </si>
+  <si>
+    <t>W-007</t>
+  </si>
+  <si>
+    <t>W-008</t>
+  </si>
+  <si>
+    <t>W-009</t>
+  </si>
+  <si>
+    <t>W-010</t>
+  </si>
+  <si>
+    <t>W-011</t>
+  </si>
+  <si>
+    <t>W-012</t>
+  </si>
+  <si>
+    <t>W-013</t>
+  </si>
+  <si>
+    <t>W-014</t>
+  </si>
+  <si>
+    <t>W-015</t>
+  </si>
+  <si>
+    <t>W-016</t>
+  </si>
+  <si>
+    <t>W-017</t>
+  </si>
+  <si>
+    <t>W-018</t>
+  </si>
+  <si>
+    <t>W-019</t>
+  </si>
+  <si>
+    <t>W-020</t>
+  </si>
+  <si>
+    <t>W-021</t>
+  </si>
+  <si>
+    <t>W-022</t>
+  </si>
+  <si>
+    <t>W-023</t>
+  </si>
+  <si>
+    <t>W-024</t>
+  </si>
+  <si>
+    <t>W-025</t>
+  </si>
+  <si>
+    <t>W-026</t>
+  </si>
+  <si>
+    <t>W-027</t>
+  </si>
+  <si>
+    <t>W-028</t>
+  </si>
+  <si>
+    <t>W-029</t>
+  </si>
+  <si>
+    <t>W-030</t>
+  </si>
+  <si>
+    <t>W-031</t>
+  </si>
+  <si>
+    <t>W-032</t>
+  </si>
+  <si>
+    <t>W-033</t>
+  </si>
+  <si>
+    <t>W-034</t>
+  </si>
+  <si>
+    <t>W-035</t>
+  </si>
+  <si>
+    <t>W-036</t>
+  </si>
+  <si>
+    <t>W-037</t>
+  </si>
+  <si>
+    <t>W-038</t>
+  </si>
+  <si>
+    <t>W-039</t>
+  </si>
+  <si>
+    <t>W-040</t>
+  </si>
+  <si>
+    <t>W-041</t>
+  </si>
+  <si>
+    <t>W-042</t>
+  </si>
+  <si>
+    <t>W-043</t>
+  </si>
+  <si>
+    <t>W-044</t>
+  </si>
+  <si>
+    <t>W-045</t>
+  </si>
+  <si>
+    <t>W-046</t>
+  </si>
+  <si>
+    <t>W-047</t>
+  </si>
+  <si>
+    <t>W-048</t>
+  </si>
+  <si>
+    <t>W-049</t>
+  </si>
+  <si>
+    <t>W-050</t>
+  </si>
+  <si>
+    <t>W-051</t>
+  </si>
+  <si>
+    <t>W-052</t>
+  </si>
+  <si>
+    <t>W-053</t>
+  </si>
+  <si>
+    <t>W-054</t>
+  </si>
+  <si>
+    <t>W-055</t>
+  </si>
+  <si>
+    <t>W-056</t>
+  </si>
+  <si>
+    <t>W-057</t>
+  </si>
+  <si>
+    <t>W-058</t>
+  </si>
+  <si>
+    <t>W-059</t>
+  </si>
+  <si>
+    <t>W-060</t>
+  </si>
+  <si>
+    <t>W-061</t>
+  </si>
+  <si>
+    <t>W-062</t>
+  </si>
+  <si>
+    <t>W-063</t>
+  </si>
+  <si>
+    <t>W-064</t>
+  </si>
+  <si>
+    <t>W-065</t>
+  </si>
+  <si>
+    <t>W-066</t>
+  </si>
+  <si>
+    <t>W-067</t>
+  </si>
+  <si>
+    <t>W-068</t>
+  </si>
+  <si>
+    <t>W-069</t>
+  </si>
+  <si>
+    <t>W-070</t>
+  </si>
+  <si>
+    <t>W-071</t>
+  </si>
+  <si>
+    <t>W-072</t>
+  </si>
+  <si>
+    <t>W-073</t>
+  </si>
+  <si>
+    <t>W-074</t>
+  </si>
+  <si>
+    <t>W-075</t>
+  </si>
+  <si>
+    <t>W-076</t>
+  </si>
+  <si>
+    <t>W-077</t>
+  </si>
+  <si>
+    <t>W-078</t>
+  </si>
+  <si>
+    <t>W-079</t>
+  </si>
+  <si>
+    <t>W-080</t>
+  </si>
+  <si>
+    <t>W-081</t>
+  </si>
+  <si>
+    <t>W-082</t>
+  </si>
+  <si>
+    <t>W-083</t>
+  </si>
+  <si>
+    <t>W-084</t>
+  </si>
+  <si>
+    <t>W-085</t>
+  </si>
+  <si>
+    <t>W-086</t>
+  </si>
+  <si>
+    <t>W-087</t>
+  </si>
+  <si>
+    <t>W-088</t>
+  </si>
+  <si>
+    <t>W-089</t>
+  </si>
+  <si>
+    <t>W-090</t>
+  </si>
+  <si>
+    <t>W-091</t>
+  </si>
+  <si>
+    <t>W-092</t>
+  </si>
+  <si>
+    <t>W-093</t>
+  </si>
+  <si>
+    <t>W-094</t>
+  </si>
+  <si>
+    <t>W-095</t>
+  </si>
+  <si>
+    <t>W-096</t>
+  </si>
+  <si>
+    <t>W-097</t>
+  </si>
+  <si>
+    <t>W-098</t>
+  </si>
+  <si>
+    <t>W-099</t>
+  </si>
+  <si>
+    <t>W-100</t>
+  </si>
+  <si>
+    <t>Top_Reservoir</t>
+  </si>
+  <si>
+    <t>Top_Seal</t>
+  </si>
+  <si>
+    <t>Central_Graben</t>
+  </si>
+  <si>
+    <t>South_Block</t>
+  </si>
+  <si>
+    <t>North_Block</t>
+  </si>
+  <si>
+    <t>production</t>
+  </si>
+  <si>
+    <t>exploration</t>
+  </si>
+  <si>
+    <t>appraisal</t>
+  </si>
+  <si>
+    <t>non_reservoir</t>
+  </si>
+  <si>
+    <t>reservoir</t>
+  </si>
+  <si>
+    <t>water</t>
+  </si>
+  <si>
+    <t>gas</t>
+  </si>
+  <si>
+    <t>oil</t>
+  </si>
+  <si>
     <t>horizon_id</t>
   </si>
   <si>
     <t>tectonic_zone</t>
-  </si>
-  <si>
-    <t>well_category</t>
-  </si>
-  <si>
-    <t>reservoir_flag</t>
-  </si>
-  <si>
-    <t>fluid_type</t>
-  </si>
-  <si>
-    <t>T_well</t>
-  </si>
-  <si>
-    <t>T_map</t>
-  </si>
-  <si>
-    <t>W-001</t>
-  </si>
-  <si>
-    <t>W-002</t>
-  </si>
-  <si>
-    <t>W-003</t>
-  </si>
-  <si>
-    <t>W-004</t>
-  </si>
-  <si>
-    <t>W-005</t>
-  </si>
-  <si>
-    <t>W-006</t>
-  </si>
-  <si>
-    <t>W-007</t>
-  </si>
-  <si>
-    <t>W-008</t>
-  </si>
-  <si>
-    <t>W-009</t>
-  </si>
-  <si>
-    <t>W-010</t>
-  </si>
-  <si>
-    <t>W-011</t>
-  </si>
-  <si>
-    <t>W-012</t>
-  </si>
-  <si>
-    <t>W-013</t>
-  </si>
-  <si>
-    <t>W-014</t>
-  </si>
-  <si>
-    <t>W-015</t>
-  </si>
-  <si>
-    <t>W-016</t>
-  </si>
-  <si>
-    <t>W-017</t>
-  </si>
-  <si>
-    <t>W-018</t>
-  </si>
-  <si>
-    <t>W-019</t>
-  </si>
-  <si>
-    <t>W-020</t>
-  </si>
-  <si>
-    <t>W-021</t>
-  </si>
-  <si>
-    <t>W-022</t>
-  </si>
-  <si>
-    <t>W-023</t>
-  </si>
-  <si>
-    <t>W-024</t>
-  </si>
-  <si>
-    <t>W-025</t>
-  </si>
-  <si>
-    <t>W-026</t>
-  </si>
-  <si>
-    <t>W-027</t>
-  </si>
-  <si>
-    <t>W-028</t>
-  </si>
-  <si>
-    <t>W-029</t>
-  </si>
-  <si>
-    <t>W-030</t>
-  </si>
-  <si>
-    <t>W-031</t>
-  </si>
-  <si>
-    <t>W-032</t>
-  </si>
-  <si>
-    <t>W-033</t>
-  </si>
-  <si>
-    <t>W-034</t>
-  </si>
-  <si>
-    <t>W-035</t>
-  </si>
-  <si>
-    <t>W-036</t>
-  </si>
-  <si>
-    <t>W-037</t>
-  </si>
-  <si>
-    <t>W-038</t>
-  </si>
-  <si>
-    <t>W-039</t>
-  </si>
-  <si>
-    <t>W-040</t>
-  </si>
-  <si>
-    <t>W-041</t>
-  </si>
-  <si>
-    <t>W-042</t>
-  </si>
-  <si>
-    <t>W-043</t>
-  </si>
-  <si>
-    <t>W-044</t>
-  </si>
-  <si>
-    <t>W-045</t>
-  </si>
-  <si>
-    <t>W-046</t>
-  </si>
-  <si>
-    <t>W-047</t>
-  </si>
-  <si>
-    <t>W-048</t>
-  </si>
-  <si>
-    <t>W-049</t>
-  </si>
-  <si>
-    <t>W-050</t>
-  </si>
-  <si>
-    <t>W-051</t>
-  </si>
-  <si>
-    <t>W-052</t>
-  </si>
-  <si>
-    <t>W-053</t>
-  </si>
-  <si>
-    <t>W-054</t>
-  </si>
-  <si>
-    <t>W-055</t>
-  </si>
-  <si>
-    <t>W-056</t>
-  </si>
-  <si>
-    <t>W-057</t>
-  </si>
-  <si>
-    <t>W-058</t>
-  </si>
-  <si>
-    <t>W-059</t>
-  </si>
-  <si>
-    <t>W-060</t>
-  </si>
-  <si>
-    <t>W-061</t>
-  </si>
-  <si>
-    <t>W-062</t>
-  </si>
-  <si>
-    <t>W-063</t>
-  </si>
-  <si>
-    <t>W-064</t>
-  </si>
-  <si>
-    <t>W-065</t>
-  </si>
-  <si>
-    <t>W-066</t>
-  </si>
-  <si>
-    <t>W-067</t>
-  </si>
-  <si>
-    <t>W-068</t>
-  </si>
-  <si>
-    <t>W-069</t>
-  </si>
-  <si>
-    <t>W-070</t>
-  </si>
-  <si>
-    <t>W-071</t>
-  </si>
-  <si>
-    <t>W-072</t>
-  </si>
-  <si>
-    <t>W-073</t>
-  </si>
-  <si>
-    <t>W-074</t>
-  </si>
-  <si>
-    <t>W-075</t>
-  </si>
-  <si>
-    <t>W-076</t>
-  </si>
-  <si>
-    <t>W-077</t>
-  </si>
-  <si>
-    <t>W-078</t>
-  </si>
-  <si>
-    <t>W-079</t>
-  </si>
-  <si>
-    <t>W-080</t>
-  </si>
-  <si>
-    <t>W-081</t>
-  </si>
-  <si>
-    <t>W-082</t>
-  </si>
-  <si>
-    <t>W-083</t>
-  </si>
-  <si>
-    <t>W-084</t>
-  </si>
-  <si>
-    <t>W-085</t>
-  </si>
-  <si>
-    <t>W-086</t>
-  </si>
-  <si>
-    <t>W-087</t>
-  </si>
-  <si>
-    <t>W-088</t>
-  </si>
-  <si>
-    <t>W-089</t>
-  </si>
-  <si>
-    <t>W-090</t>
-  </si>
-  <si>
-    <t>W-091</t>
-  </si>
-  <si>
-    <t>W-092</t>
-  </si>
-  <si>
-    <t>W-093</t>
-  </si>
-  <si>
-    <t>W-094</t>
-  </si>
-  <si>
-    <t>W-095</t>
-  </si>
-  <si>
-    <t>W-096</t>
-  </si>
-  <si>
-    <t>W-097</t>
-  </si>
-  <si>
-    <t>W-098</t>
-  </si>
-  <si>
-    <t>W-099</t>
-  </si>
-  <si>
-    <t>W-100</t>
-  </si>
-  <si>
-    <t>Top_Reservoir</t>
-  </si>
-  <si>
-    <t>Top_Seal</t>
-  </si>
-  <si>
-    <t>Central_Graben</t>
-  </si>
-  <si>
-    <t>South_Block</t>
-  </si>
-  <si>
-    <t>North_Block</t>
-  </si>
-  <si>
-    <t>production</t>
-  </si>
-  <si>
-    <t>exploration</t>
-  </si>
-  <si>
-    <t>appraisal</t>
-  </si>
-  <si>
-    <t>non_reservoir</t>
-  </si>
-  <si>
-    <t>reservoir</t>
-  </si>
-  <si>
-    <t>water</t>
-  </si>
-  <si>
-    <t>gas</t>
-  </si>
-  <si>
-    <t>oil</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -428,17 +434,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -476,7 +490,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -510,6 +524,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -544,9 +559,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -719,11 +735,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L101"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -740,30 +756,30 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G1" t="s">
+        <v>124</v>
+      </c>
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
         <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" t="s">
-        <v>12</v>
       </c>
       <c r="B2">
         <v>7501.1</v>
@@ -772,25 +788,25 @@
         <v>9671.5</v>
       </c>
       <c r="D2">
-        <v>2319.03</v>
+        <v>2319.0300000000002</v>
       </c>
       <c r="E2">
         <v>2300.1</v>
       </c>
       <c r="F2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G2" t="s">
         <v>112</v>
       </c>
-      <c r="G2" t="s">
-        <v>114</v>
-      </c>
       <c r="H2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K2">
         <v>1713.24</v>
@@ -799,9 +815,9 @@
         <v>1791.03</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B3">
         <v>10766.6</v>
@@ -810,25 +826,25 @@
         <v>6577.6</v>
       </c>
       <c r="D3">
-        <v>2485.68</v>
+        <v>2485.6799999999998</v>
       </c>
       <c r="E3">
-        <v>2458.07</v>
+        <v>2458.0700000000002</v>
       </c>
       <c r="F3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K3">
         <v>1768.15</v>
@@ -837,12 +853,12 @@
         <v>1781.45</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B4">
-        <v>9308.200000000001</v>
+        <v>9308.2000000000007</v>
       </c>
       <c r="C4">
         <v>4282.2</v>
@@ -854,19 +870,19 @@
         <v>2560.42</v>
       </c>
       <c r="F4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H4" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I4" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K4">
         <v>1866.42</v>
@@ -875,15 +891,15 @@
         <v>1821.17</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B5">
         <v>2702.5</v>
       </c>
       <c r="C5">
-        <v>5237.4</v>
+        <v>5237.3999999999996</v>
       </c>
       <c r="D5">
         <v>2260.54</v>
@@ -892,19 +908,19 @@
         <v>2206.89</v>
       </c>
       <c r="F5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K5">
         <v>1722.59</v>
@@ -913,9 +929,9 @@
         <v>1658.2</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>3602</v>
@@ -924,25 +940,25 @@
         <v>8728.1</v>
       </c>
       <c r="D6">
-        <v>2327.43</v>
+        <v>2327.4299999999998</v>
       </c>
       <c r="E6">
-        <v>2342.18</v>
+        <v>2342.1799999999998</v>
       </c>
       <c r="F6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G6" t="s">
+        <v>114</v>
+      </c>
+      <c r="H6" t="s">
         <v>116</v>
       </c>
-      <c r="H6" t="s">
-        <v>118</v>
-      </c>
       <c r="I6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K6">
         <v>1730.67</v>
@@ -951,9 +967,9 @@
         <v>1704.4</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B7">
         <v>10482.6</v>
@@ -968,19 +984,19 @@
         <v>2579.75</v>
       </c>
       <c r="F7" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I7" t="s">
+        <v>119</v>
+      </c>
+      <c r="J7" t="s">
         <v>121</v>
-      </c>
-      <c r="J7" t="s">
-        <v>123</v>
       </c>
       <c r="K7">
         <v>1860.82</v>
@@ -989,9 +1005,9 @@
         <v>1926.7</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B8">
         <v>63.2</v>
@@ -1006,19 +1022,19 @@
         <v>2254.4</v>
       </c>
       <c r="F8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H8" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I8" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K8">
         <v>1747.89</v>
@@ -1027,36 +1043,36 @@
         <v>1731.71</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B9">
-        <v>9854.700000000001</v>
+        <v>9854.7000000000007</v>
       </c>
       <c r="C9">
         <v>6836.8</v>
       </c>
       <c r="D9">
-        <v>2485.49</v>
+        <v>2485.4899999999998</v>
       </c>
       <c r="E9">
         <v>2464.94</v>
       </c>
       <c r="F9" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G9" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H9" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I9" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K9">
         <v>1851.1</v>
@@ -1065,12 +1081,12 @@
         <v>1835.46</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B10">
-        <v>9564.799999999999</v>
+        <v>9564.7999999999993</v>
       </c>
       <c r="C10">
         <v>3554.1</v>
@@ -1082,19 +1098,19 @@
         <v>2541.52</v>
       </c>
       <c r="F10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G10" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H10" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I10" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K10">
         <v>1869.46</v>
@@ -1103,9 +1119,9 @@
         <v>1903.56</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11">
         <v>5615.2</v>
@@ -1114,25 +1130,25 @@
         <v>5191</v>
       </c>
       <c r="D11">
-        <v>2379.26</v>
+        <v>2379.2600000000002</v>
       </c>
       <c r="E11">
         <v>2377.92</v>
       </c>
       <c r="F11" t="s">
+        <v>110</v>
+      </c>
+      <c r="G11" t="s">
         <v>112</v>
       </c>
-      <c r="G11" t="s">
-        <v>114</v>
-      </c>
       <c r="H11" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J11" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K11">
         <v>1785.21</v>
@@ -1141,9 +1157,9 @@
         <v>1743.86</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B12">
         <v>3636.4</v>
@@ -1158,19 +1174,19 @@
         <v>2277.94</v>
       </c>
       <c r="F12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I12" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K12">
         <v>1699.46</v>
@@ -1179,15 +1195,15 @@
         <v>1663.65</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B13">
         <v>3341.1</v>
       </c>
       <c r="C13">
-        <v>9091.799999999999</v>
+        <v>9091.7999999999993</v>
       </c>
       <c r="D13">
         <v>2325.29</v>
@@ -1196,19 +1212,19 @@
         <v>2337.52</v>
       </c>
       <c r="F13" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G13" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H13" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I13" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J13" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K13">
         <v>1763.69</v>
@@ -1217,9 +1233,9 @@
         <v>1757.22</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B14">
         <v>3058.4</v>
@@ -1234,19 +1250,19 @@
         <v>2462.48</v>
       </c>
       <c r="F14" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G14" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H14" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I14" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J14" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K14">
         <v>1742.01</v>
@@ -1255,15 +1271,15 @@
         <v>1822.06</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B15">
         <v>5340.9</v>
       </c>
       <c r="C15">
-        <v>9334.200000000001</v>
+        <v>9334.2000000000007</v>
       </c>
       <c r="D15">
         <v>2324.66</v>
@@ -1272,19 +1288,19 @@
         <v>2285.13</v>
       </c>
       <c r="F15" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G15" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I15" t="s">
+        <v>119</v>
+      </c>
+      <c r="J15" t="s">
         <v>121</v>
-      </c>
-      <c r="J15" t="s">
-        <v>123</v>
       </c>
       <c r="K15">
         <v>1728.57</v>
@@ -1293,9 +1309,9 @@
         <v>1684.49</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B16">
         <v>6054.6</v>
@@ -1310,19 +1326,19 @@
         <v>2458.98</v>
       </c>
       <c r="F16" t="s">
+        <v>110</v>
+      </c>
+      <c r="G16" t="s">
         <v>112</v>
       </c>
-      <c r="G16" t="s">
-        <v>114</v>
-      </c>
       <c r="H16" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I16" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J16" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K16">
         <v>1805</v>
@@ -1331,9 +1347,9 @@
         <v>1828.59</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B17">
         <v>6642</v>
@@ -1342,25 +1358,25 @@
         <v>7529.8</v>
       </c>
       <c r="D17">
-        <v>2362.32</v>
+        <v>2362.3200000000002</v>
       </c>
       <c r="E17">
         <v>2235.16</v>
       </c>
       <c r="F17" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G17" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H17" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I17" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J17" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K17">
         <v>1711.34</v>
@@ -1369,9 +1385,9 @@
         <v>1742.97</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B18">
         <v>11946</v>
@@ -1380,25 +1396,25 @@
         <v>8105.3</v>
       </c>
       <c r="D18">
-        <v>2472.95</v>
+        <v>2472.9499999999998</v>
       </c>
       <c r="E18">
         <v>2481.37</v>
       </c>
       <c r="F18" t="s">
+        <v>111</v>
+      </c>
+      <c r="G18" t="s">
         <v>113</v>
       </c>
-      <c r="G18" t="s">
-        <v>115</v>
-      </c>
       <c r="H18" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I18" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J18" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K18">
         <v>1813.15</v>
@@ -1407,9 +1423,9 @@
         <v>1800.82</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B19">
         <v>9511.9</v>
@@ -1421,22 +1437,22 @@
         <v>2506.84</v>
       </c>
       <c r="E19">
-        <v>2468.45</v>
+        <v>2468.4499999999998</v>
       </c>
       <c r="F19" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G19" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H19" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I19" t="s">
+        <v>119</v>
+      </c>
+      <c r="J19" t="s">
         <v>121</v>
-      </c>
-      <c r="J19" t="s">
-        <v>123</v>
       </c>
       <c r="K19">
         <v>1877.79</v>
@@ -1445,9 +1461,9 @@
         <v>1820.95</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B20">
         <v>7466.2</v>
@@ -1459,22 +1475,22 @@
         <v>2485.79</v>
       </c>
       <c r="E20">
-        <v>2352.8</v>
+        <v>2352.8000000000002</v>
       </c>
       <c r="F20" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G20" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H20" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I20" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J20" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K20">
         <v>1813.67</v>
@@ -1483,9 +1499,9 @@
         <v>1765.32</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B21">
         <v>11867.5</v>
@@ -1500,19 +1516,19 @@
         <v>2515.21</v>
       </c>
       <c r="F21" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G21" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H21" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I21" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J21" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K21">
         <v>1789.04</v>
@@ -1521,15 +1537,15 @@
         <v>1855.94</v>
       </c>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B22">
-        <v>2583.7</v>
+        <v>2583.6999999999998</v>
       </c>
       <c r="C22">
-        <v>142.7</v>
+        <v>142.69999999999999</v>
       </c>
       <c r="D22">
         <v>2457.11</v>
@@ -1538,19 +1554,19 @@
         <v>2441.15</v>
       </c>
       <c r="F22" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G22" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H22" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I22" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J22" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K22">
         <v>1805.4</v>
@@ -1559,9 +1575,9 @@
         <v>1837.22</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B23">
         <v>1922.5</v>
@@ -1573,22 +1589,22 @@
         <v>2249.67</v>
       </c>
       <c r="E23">
-        <v>2274.57</v>
+        <v>2274.5700000000002</v>
       </c>
       <c r="F23" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G23" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H23" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I23" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J23" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K23">
         <v>1719.56</v>
@@ -1597,9 +1613,9 @@
         <v>1732</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B24">
         <v>7350.5</v>
@@ -1608,25 +1624,25 @@
         <v>7930.2</v>
       </c>
       <c r="D24">
-        <v>2361.49</v>
+        <v>2361.4899999999998</v>
       </c>
       <c r="E24">
-        <v>2471.57</v>
+        <v>2471.5700000000002</v>
       </c>
       <c r="F24" t="s">
+        <v>110</v>
+      </c>
+      <c r="G24" t="s">
         <v>112</v>
       </c>
-      <c r="G24" t="s">
-        <v>114</v>
-      </c>
       <c r="H24" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I24" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J24" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K24">
         <v>1762.46</v>
@@ -1635,12 +1651,12 @@
         <v>1867.03</v>
       </c>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B25">
-        <v>527.3</v>
+        <v>527.29999999999995</v>
       </c>
       <c r="C25">
         <v>5130</v>
@@ -1649,22 +1665,22 @@
         <v>2260.5</v>
       </c>
       <c r="E25">
-        <v>2267.82</v>
+        <v>2267.8200000000002</v>
       </c>
       <c r="F25" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G25" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H25" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I25" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J25" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K25">
         <v>1702.52</v>
@@ -1673,9 +1689,9 @@
         <v>1676.71</v>
       </c>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B26">
         <v>428.2</v>
@@ -1690,19 +1706,19 @@
         <v>2245.6</v>
       </c>
       <c r="F26" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G26" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H26" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I26" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J26" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K26">
         <v>1649.23</v>
@@ -1711,15 +1727,15 @@
         <v>1677</v>
       </c>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B27">
         <v>6178.7</v>
       </c>
       <c r="C27">
-        <v>2264.2</v>
+        <v>2264.1999999999998</v>
       </c>
       <c r="D27">
         <v>2433.75</v>
@@ -1728,19 +1744,19 @@
         <v>2575.77</v>
       </c>
       <c r="F27" t="s">
+        <v>110</v>
+      </c>
+      <c r="G27" t="s">
         <v>112</v>
       </c>
-      <c r="G27" t="s">
-        <v>114</v>
-      </c>
       <c r="H27" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I27" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J27" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K27">
         <v>1809.04</v>
@@ -1749,9 +1765,9 @@
         <v>1899.28</v>
       </c>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B28">
         <v>5594.5</v>
@@ -1760,25 +1776,25 @@
         <v>1985.2</v>
       </c>
       <c r="D28">
-        <v>2443.45</v>
+        <v>2443.4499999999998</v>
       </c>
       <c r="E28">
         <v>2428.46</v>
       </c>
       <c r="F28" t="s">
+        <v>110</v>
+      </c>
+      <c r="G28" t="s">
         <v>112</v>
       </c>
-      <c r="G28" t="s">
-        <v>114</v>
-      </c>
       <c r="H28" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I28" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J28" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K28">
         <v>1813.72</v>
@@ -1787,9 +1803,9 @@
         <v>1776.49</v>
       </c>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B29">
         <v>11006</v>
@@ -1804,19 +1820,19 @@
         <v>2517.71</v>
       </c>
       <c r="F29" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H29" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I29" t="s">
+        <v>119</v>
+      </c>
+      <c r="J29" t="s">
         <v>121</v>
-      </c>
-      <c r="J29" t="s">
-        <v>123</v>
       </c>
       <c r="K29">
         <v>1885.5</v>
@@ -1825,9 +1841,9 @@
         <v>1818.66</v>
       </c>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B30">
         <v>7550.7</v>
@@ -1836,25 +1852,25 @@
         <v>1794.1</v>
       </c>
       <c r="D30">
-        <v>2467.49</v>
+        <v>2467.4899999999998</v>
       </c>
       <c r="E30">
-        <v>2306.8</v>
+        <v>2306.8000000000002</v>
       </c>
       <c r="F30" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G30" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H30" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I30" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J30" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K30">
         <v>1853.22</v>
@@ -1863,9 +1879,9 @@
         <v>1726.15</v>
       </c>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B31">
         <v>6169.4</v>
@@ -1880,19 +1896,19 @@
         <v>2432.41</v>
       </c>
       <c r="F31" t="s">
+        <v>110</v>
+      </c>
+      <c r="G31" t="s">
         <v>112</v>
       </c>
-      <c r="G31" t="s">
-        <v>114</v>
-      </c>
       <c r="H31" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I31" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J31" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K31">
         <v>1812.14</v>
@@ -1901,15 +1917,15 @@
         <v>1807.89</v>
       </c>
     </row>
-    <row r="32" spans="1:12">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B32">
         <v>5962.5</v>
       </c>
       <c r="C32">
-        <v>9481.200000000001</v>
+        <v>9481.2000000000007</v>
       </c>
       <c r="D32">
         <v>2314.11</v>
@@ -1918,19 +1934,19 @@
         <v>2420.46</v>
       </c>
       <c r="F32" t="s">
+        <v>110</v>
+      </c>
+      <c r="G32" t="s">
         <v>112</v>
       </c>
-      <c r="G32" t="s">
-        <v>114</v>
-      </c>
       <c r="H32" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I32" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J32" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K32">
         <v>1687.72</v>
@@ -1939,9 +1955,9 @@
         <v>1770.24</v>
       </c>
     </row>
-    <row r="33" spans="1:12">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B33">
         <v>2970.2</v>
@@ -1950,25 +1966,25 @@
         <v>5733.3</v>
       </c>
       <c r="D33">
-        <v>2265.05</v>
+        <v>2265.0500000000002</v>
       </c>
       <c r="E33">
         <v>2315.61</v>
       </c>
       <c r="F33" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G33" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H33" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I33" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J33" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K33">
         <v>1666.57</v>
@@ -1977,9 +1993,9 @@
         <v>1754.48</v>
       </c>
     </row>
-    <row r="34" spans="1:12">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B34">
         <v>141.5</v>
@@ -1988,25 +2004,25 @@
         <v>3400.7</v>
       </c>
       <c r="D34">
-        <v>2288.22</v>
+        <v>2288.2199999999998</v>
       </c>
       <c r="E34">
         <v>2269.96</v>
       </c>
       <c r="F34" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G34" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H34" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I34" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J34" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K34">
         <v>1688.28</v>
@@ -2015,12 +2031,12 @@
         <v>1758.96</v>
       </c>
     </row>
-    <row r="35" spans="1:12">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B35">
-        <v>2308.8</v>
+        <v>2308.8000000000002</v>
       </c>
       <c r="C35">
         <v>2715.2</v>
@@ -2032,19 +2048,19 @@
         <v>2292.14</v>
       </c>
       <c r="F35" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G35" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H35" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I35" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J35" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K35">
         <v>1759.07</v>
@@ -2053,9 +2069,9 @@
         <v>1654.04</v>
       </c>
     </row>
-    <row r="36" spans="1:12">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B36">
         <v>8304.4</v>
@@ -2070,19 +2086,19 @@
         <v>2273.35</v>
       </c>
       <c r="F36" t="s">
+        <v>111</v>
+      </c>
+      <c r="G36" t="s">
         <v>113</v>
       </c>
-      <c r="G36" t="s">
-        <v>115</v>
-      </c>
       <c r="H36" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I36" t="s">
+        <v>119</v>
+      </c>
+      <c r="J36" t="s">
         <v>121</v>
-      </c>
-      <c r="J36" t="s">
-        <v>123</v>
       </c>
       <c r="K36">
         <v>1714.47</v>
@@ -2091,12 +2107,12 @@
         <v>1625.27</v>
       </c>
     </row>
-    <row r="37" spans="1:12">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B37">
-        <v>2407.3</v>
+        <v>2407.3000000000002</v>
       </c>
       <c r="C37">
         <v>4444.8</v>
@@ -2105,22 +2121,22 @@
         <v>2282.33</v>
       </c>
       <c r="E37">
-        <v>2290.55</v>
+        <v>2290.5500000000002</v>
       </c>
       <c r="F37" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G37" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H37" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I37" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J37" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K37">
         <v>1749.66</v>
@@ -2129,12 +2145,12 @@
         <v>1746.78</v>
       </c>
     </row>
-    <row r="38" spans="1:12">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B38">
-        <v>4434.4</v>
+        <v>4434.3999999999996</v>
       </c>
       <c r="C38">
         <v>9803.9</v>
@@ -2143,22 +2159,22 @@
         <v>2325.15</v>
       </c>
       <c r="E38">
-        <v>2308.47</v>
+        <v>2308.4699999999998</v>
       </c>
       <c r="F38" t="s">
+        <v>110</v>
+      </c>
+      <c r="G38" t="s">
         <v>112</v>
       </c>
-      <c r="G38" t="s">
-        <v>114</v>
-      </c>
       <c r="H38" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I38" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J38" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K38">
         <v>1744.29</v>
@@ -2167,9 +2183,9 @@
         <v>1699.35</v>
       </c>
     </row>
-    <row r="39" spans="1:12">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B39">
         <v>44.8</v>
@@ -2184,19 +2200,19 @@
         <v>2285.84</v>
       </c>
       <c r="F39" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G39" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H39" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I39" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J39" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K39">
         <v>1722.67</v>
@@ -2205,9 +2221,9 @@
         <v>1770.16</v>
       </c>
     </row>
-    <row r="40" spans="1:12">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B40">
         <v>9960.6</v>
@@ -2216,25 +2232,25 @@
         <v>5211.7</v>
       </c>
       <c r="D40">
-        <v>2511.22</v>
+        <v>2511.2199999999998</v>
       </c>
       <c r="E40">
-        <v>2516.01</v>
+        <v>2516.0100000000002</v>
       </c>
       <c r="F40" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G40" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H40" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I40" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J40" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K40">
         <v>1856.1</v>
@@ -2243,9 +2259,9 @@
         <v>1944.29</v>
       </c>
     </row>
-    <row r="41" spans="1:12">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B41">
         <v>1853.5</v>
@@ -2257,22 +2273,22 @@
         <v>2288.21</v>
       </c>
       <c r="E41">
-        <v>2263.22</v>
+        <v>2263.2199999999998</v>
       </c>
       <c r="F41" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G41" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H41" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I41" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J41" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K41">
         <v>1726.86</v>
@@ -2281,9 +2297,9 @@
         <v>1698.85</v>
       </c>
     </row>
-    <row r="42" spans="1:12">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B42">
         <v>3211.2</v>
@@ -2295,22 +2311,22 @@
         <v>2295.41</v>
       </c>
       <c r="E42">
-        <v>2286.05</v>
+        <v>2286.0500000000002</v>
       </c>
       <c r="F42" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G42" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H42" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I42" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J42" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K42">
         <v>1683.8</v>
@@ -2319,9 +2335,9 @@
         <v>1702.4</v>
       </c>
     </row>
-    <row r="43" spans="1:12">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B43">
         <v>10564</v>
@@ -2330,25 +2346,25 @@
         <v>5806.5</v>
       </c>
       <c r="D43">
-        <v>2506.97</v>
+        <v>2506.9699999999998</v>
       </c>
       <c r="E43">
-        <v>2509.2</v>
+        <v>2509.1999999999998</v>
       </c>
       <c r="F43" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G43" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H43" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I43" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J43" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K43">
         <v>1899.55</v>
@@ -2357,9 +2373,9 @@
         <v>1834.66</v>
       </c>
     </row>
-    <row r="44" spans="1:12">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B44">
         <v>6117.5</v>
@@ -2374,19 +2390,19 @@
         <v>2397.37</v>
       </c>
       <c r="F44" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G44" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H44" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I44" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J44" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K44">
         <v>1825.81</v>
@@ -2395,12 +2411,12 @@
         <v>1786.77</v>
       </c>
     </row>
-    <row r="45" spans="1:12">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B45">
-        <v>10165.8</v>
+        <v>10165.799999999999</v>
       </c>
       <c r="C45">
         <v>8781.9</v>
@@ -2412,19 +2428,19 @@
         <v>2414.66</v>
       </c>
       <c r="F45" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G45" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H45" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I45" t="s">
+        <v>119</v>
+      </c>
+      <c r="J45" t="s">
         <v>121</v>
-      </c>
-      <c r="J45" t="s">
-        <v>123</v>
       </c>
       <c r="K45">
         <v>1821.31</v>
@@ -2433,9 +2449,9 @@
         <v>1783.86</v>
       </c>
     </row>
-    <row r="46" spans="1:12">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B46">
         <v>7676.6</v>
@@ -2450,19 +2466,19 @@
         <v>2634.64</v>
       </c>
       <c r="F46" t="s">
+        <v>110</v>
+      </c>
+      <c r="G46" t="s">
         <v>112</v>
       </c>
-      <c r="G46" t="s">
-        <v>114</v>
-      </c>
       <c r="H46" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I46" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J46" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K46">
         <v>1809.07</v>
@@ -2471,12 +2487,12 @@
         <v>1865.44</v>
       </c>
     </row>
-    <row r="47" spans="1:12">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B47">
-        <v>8901.299999999999</v>
+        <v>8901.2999999999993</v>
       </c>
       <c r="C47">
         <v>9227.6</v>
@@ -2485,22 +2501,22 @@
         <v>2349.06</v>
       </c>
       <c r="E47">
-        <v>2374.55</v>
+        <v>2374.5500000000002</v>
       </c>
       <c r="F47" t="s">
+        <v>111</v>
+      </c>
+      <c r="G47" t="s">
         <v>113</v>
       </c>
-      <c r="G47" t="s">
-        <v>115</v>
-      </c>
       <c r="H47" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I47" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J47" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K47">
         <v>1701.05</v>
@@ -2509,12 +2525,12 @@
         <v>1779.53</v>
       </c>
     </row>
-    <row r="48" spans="1:12">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B48">
-        <v>1097.9</v>
+        <v>1097.9000000000001</v>
       </c>
       <c r="C48">
         <v>687.2</v>
@@ -2523,22 +2539,22 @@
         <v>2390.37</v>
       </c>
       <c r="E48">
-        <v>2394.49</v>
+        <v>2394.4899999999998</v>
       </c>
       <c r="F48" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G48" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H48" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I48" t="s">
+        <v>119</v>
+      </c>
+      <c r="J48" t="s">
         <v>121</v>
-      </c>
-      <c r="J48" t="s">
-        <v>123</v>
       </c>
       <c r="K48">
         <v>1732.24</v>
@@ -2547,9 +2563,9 @@
         <v>1700.37</v>
       </c>
     </row>
-    <row r="49" spans="1:12">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B49">
         <v>6493.7</v>
@@ -2558,25 +2574,25 @@
         <v>4300</v>
       </c>
       <c r="D49">
-        <v>2442.24</v>
+        <v>2442.2399999999998</v>
       </c>
       <c r="E49">
         <v>2318.36</v>
       </c>
       <c r="F49" t="s">
+        <v>110</v>
+      </c>
+      <c r="G49" t="s">
         <v>112</v>
       </c>
-      <c r="G49" t="s">
-        <v>114</v>
-      </c>
       <c r="H49" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I49" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J49" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K49">
         <v>1771.79</v>
@@ -2585,36 +2601,36 @@
         <v>1748.59</v>
       </c>
     </row>
-    <row r="50" spans="1:12">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B50">
         <v>6093.3</v>
       </c>
       <c r="C50">
-        <v>5195.1</v>
+        <v>5195.1000000000004</v>
       </c>
       <c r="D50">
-        <v>2420.2</v>
+        <v>2420.1999999999998</v>
       </c>
       <c r="E50">
-        <v>2447.74</v>
+        <v>2447.7399999999998</v>
       </c>
       <c r="F50" t="s">
+        <v>110</v>
+      </c>
+      <c r="G50" t="s">
         <v>112</v>
       </c>
-      <c r="G50" t="s">
-        <v>114</v>
-      </c>
       <c r="H50" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I50" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J50" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K50">
         <v>1812.13</v>
@@ -2623,9 +2639,9 @@
         <v>1806.65</v>
       </c>
     </row>
-    <row r="51" spans="1:12">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B51">
         <v>10456.1</v>
@@ -2634,25 +2650,25 @@
         <v>9509.4</v>
       </c>
       <c r="D51">
-        <v>2402.05</v>
+        <v>2402.0500000000002</v>
       </c>
       <c r="E51">
         <v>2343.16</v>
       </c>
       <c r="F51" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G51" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H51" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I51" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J51" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K51">
         <v>1803.02</v>
@@ -2661,9 +2677,9 @@
         <v>1795.71</v>
       </c>
     </row>
-    <row r="52" spans="1:12">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B52">
         <v>4335.2</v>
@@ -2678,19 +2694,19 @@
         <v>2220.25</v>
       </c>
       <c r="F52" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G52" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H52" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I52" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J52" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K52">
         <v>1810.48</v>
@@ -2699,9 +2715,9 @@
         <v>1686.45</v>
       </c>
     </row>
-    <row r="53" spans="1:12">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B53">
         <v>7178.2</v>
@@ -2713,22 +2729,22 @@
         <v>2358.94</v>
       </c>
       <c r="E53">
-        <v>2420.05</v>
+        <v>2420.0500000000002</v>
       </c>
       <c r="F53" t="s">
+        <v>110</v>
+      </c>
+      <c r="G53" t="s">
         <v>112</v>
       </c>
-      <c r="G53" t="s">
-        <v>114</v>
-      </c>
       <c r="H53" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I53" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J53" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K53">
         <v>1813.39</v>
@@ -2737,9 +2753,9 @@
         <v>1806.29</v>
       </c>
     </row>
-    <row r="54" spans="1:12">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B54">
         <v>711</v>
@@ -2754,19 +2770,19 @@
         <v>2248.44</v>
       </c>
       <c r="F54" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G54" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H54" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I54" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J54" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K54">
         <v>1700.77</v>
@@ -2775,12 +2791,12 @@
         <v>1661.06</v>
       </c>
     </row>
-    <row r="55" spans="1:12">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B55">
-        <v>4651.6</v>
+        <v>4651.6000000000004</v>
       </c>
       <c r="C55">
         <v>7170.9</v>
@@ -2792,19 +2808,19 @@
         <v>2293.39</v>
       </c>
       <c r="F55" t="s">
+        <v>110</v>
+      </c>
+      <c r="G55" t="s">
         <v>112</v>
       </c>
-      <c r="G55" t="s">
-        <v>114</v>
-      </c>
       <c r="H55" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I55" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J55" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K55">
         <v>1737.01</v>
@@ -2813,9 +2829,9 @@
         <v>1726.98</v>
       </c>
     </row>
-    <row r="56" spans="1:12">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B56">
         <v>3876.4</v>
@@ -2830,19 +2846,19 @@
         <v>2186.75</v>
       </c>
       <c r="F56" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G56" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H56" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I56" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J56" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K56">
         <v>1712.57</v>
@@ -2851,9 +2867,9 @@
         <v>1690.48</v>
       </c>
     </row>
-    <row r="57" spans="1:12">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B57">
         <v>1802.4</v>
@@ -2868,19 +2884,19 @@
         <v>2280.83</v>
       </c>
       <c r="F57" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G57" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H57" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I57" t="s">
+        <v>119</v>
+      </c>
+      <c r="J57" t="s">
         <v>121</v>
-      </c>
-      <c r="J57" t="s">
-        <v>123</v>
       </c>
       <c r="K57">
         <v>1707.95</v>
@@ -2889,9 +2905,9 @@
         <v>1751.37</v>
       </c>
     </row>
-    <row r="58" spans="1:12">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B58">
         <v>9796.1</v>
@@ -2900,25 +2916,25 @@
         <v>3326.8</v>
       </c>
       <c r="D58">
-        <v>2530.57</v>
+        <v>2530.5700000000002</v>
       </c>
       <c r="E58">
         <v>2508.27</v>
       </c>
       <c r="F58" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G58" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H58" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I58" t="s">
+        <v>119</v>
+      </c>
+      <c r="J58" t="s">
         <v>121</v>
-      </c>
-      <c r="J58" t="s">
-        <v>123</v>
       </c>
       <c r="K58">
         <v>1814.87</v>
@@ -2927,12 +2943,12 @@
         <v>1838.82</v>
       </c>
     </row>
-    <row r="59" spans="1:12">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B59">
-        <v>4553.4</v>
+        <v>4553.3999999999996</v>
       </c>
       <c r="C59">
         <v>3982.8</v>
@@ -2944,19 +2960,19 @@
         <v>2396.25</v>
       </c>
       <c r="F59" t="s">
+        <v>110</v>
+      </c>
+      <c r="G59" t="s">
         <v>112</v>
       </c>
-      <c r="G59" t="s">
-        <v>114</v>
-      </c>
       <c r="H59" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I59" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J59" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K59">
         <v>1765.43</v>
@@ -2965,9 +2981,9 @@
         <v>1834.27</v>
       </c>
     </row>
-    <row r="60" spans="1:12">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B60">
         <v>11745</v>
@@ -2976,25 +2992,25 @@
         <v>2029.1</v>
       </c>
       <c r="D60">
-        <v>2571.26</v>
+        <v>2571.2600000000002</v>
       </c>
       <c r="E60">
         <v>2631.41</v>
       </c>
       <c r="F60" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G60" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H60" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I60" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J60" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K60">
         <v>1875.28</v>
@@ -3003,9 +3019,9 @@
         <v>1944.21</v>
       </c>
     </row>
-    <row r="61" spans="1:12">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B61">
         <v>7079.9</v>
@@ -3020,19 +3036,19 @@
         <v>2481.83</v>
       </c>
       <c r="F61" t="s">
+        <v>110</v>
+      </c>
+      <c r="G61" t="s">
         <v>112</v>
       </c>
-      <c r="G61" t="s">
-        <v>114</v>
-      </c>
       <c r="H61" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I61" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J61" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K61">
         <v>1801.81</v>
@@ -3041,9 +3057,9 @@
         <v>1796.68</v>
       </c>
     </row>
-    <row r="62" spans="1:12">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B62">
         <v>7260.7</v>
@@ -3058,19 +3074,19 @@
         <v>2407.21</v>
       </c>
       <c r="F62" t="s">
+        <v>110</v>
+      </c>
+      <c r="G62" t="s">
         <v>112</v>
       </c>
-      <c r="G62" t="s">
-        <v>114</v>
-      </c>
       <c r="H62" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I62" t="s">
+        <v>119</v>
+      </c>
+      <c r="J62" t="s">
         <v>121</v>
-      </c>
-      <c r="J62" t="s">
-        <v>123</v>
       </c>
       <c r="K62">
         <v>1790.01</v>
@@ -3079,9 +3095,9 @@
         <v>1690.56</v>
       </c>
     </row>
-    <row r="63" spans="1:12">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B63">
         <v>7656</v>
@@ -3096,19 +3112,19 @@
         <v>2241.35</v>
       </c>
       <c r="F63" t="s">
+        <v>110</v>
+      </c>
+      <c r="G63" t="s">
         <v>112</v>
       </c>
-      <c r="G63" t="s">
-        <v>114</v>
-      </c>
       <c r="H63" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I63" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J63" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K63">
         <v>1751.85</v>
@@ -3117,36 +3133,36 @@
         <v>1651.59</v>
       </c>
     </row>
-    <row r="64" spans="1:12">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B64">
         <v>8117.4</v>
       </c>
       <c r="C64">
-        <v>8401.700000000001</v>
+        <v>8401.7000000000007</v>
       </c>
       <c r="D64">
         <v>2364.14</v>
       </c>
       <c r="E64">
-        <v>2358.72</v>
+        <v>2358.7199999999998</v>
       </c>
       <c r="F64" t="s">
+        <v>110</v>
+      </c>
+      <c r="G64" t="s">
         <v>112</v>
       </c>
-      <c r="G64" t="s">
-        <v>114</v>
-      </c>
       <c r="H64" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I64" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J64" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K64">
         <v>1793.73</v>
@@ -3155,36 +3171,36 @@
         <v>1758.31</v>
       </c>
     </row>
-    <row r="65" spans="1:12">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B65">
         <v>1809.5</v>
       </c>
       <c r="C65">
-        <v>1124.1</v>
+        <v>1124.0999999999999</v>
       </c>
       <c r="D65">
-        <v>2405.53</v>
+        <v>2405.5300000000002</v>
       </c>
       <c r="E65">
         <v>2388.94</v>
       </c>
       <c r="F65" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G65" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H65" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I65" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J65" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K65">
         <v>1782.89</v>
@@ -3193,9 +3209,9 @@
         <v>1777.79</v>
       </c>
     </row>
-    <row r="66" spans="1:12">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B66">
         <v>5283.8</v>
@@ -3210,19 +3226,19 @@
         <v>2278.69</v>
       </c>
       <c r="F66" t="s">
+        <v>110</v>
+      </c>
+      <c r="G66" t="s">
         <v>112</v>
       </c>
-      <c r="G66" t="s">
-        <v>114</v>
-      </c>
       <c r="H66" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I66" t="s">
+        <v>119</v>
+      </c>
+      <c r="J66" t="s">
         <v>121</v>
-      </c>
-      <c r="J66" t="s">
-        <v>123</v>
       </c>
       <c r="K66">
         <v>1766.33</v>
@@ -3231,9 +3247,9 @@
         <v>1701.71</v>
       </c>
     </row>
-    <row r="67" spans="1:12">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B67">
         <v>2874.8</v>
@@ -3242,25 +3258,25 @@
         <v>4792</v>
       </c>
       <c r="D67">
-        <v>2284.05</v>
+        <v>2284.0500000000002</v>
       </c>
       <c r="E67">
-        <v>2284.01</v>
+        <v>2284.0100000000002</v>
       </c>
       <c r="F67" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G67" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H67" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I67" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J67" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K67">
         <v>1700.76</v>
@@ -3269,9 +3285,9 @@
         <v>1699.94</v>
       </c>
     </row>
-    <row r="68" spans="1:12">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B68">
         <v>4830</v>
@@ -3280,25 +3296,25 @@
         <v>5946.8</v>
       </c>
       <c r="D68">
-        <v>2340.2</v>
+        <v>2340.1999999999998</v>
       </c>
       <c r="E68">
-        <v>2254.53</v>
+        <v>2254.5300000000002</v>
       </c>
       <c r="F68" t="s">
+        <v>110</v>
+      </c>
+      <c r="G68" t="s">
         <v>112</v>
       </c>
-      <c r="G68" t="s">
-        <v>114</v>
-      </c>
       <c r="H68" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I68" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J68" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K68">
         <v>1739.19</v>
@@ -3307,36 +3323,36 @@
         <v>1723.27</v>
       </c>
     </row>
-    <row r="69" spans="1:12">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B69">
-        <v>1160.4</v>
+        <v>1160.4000000000001</v>
       </c>
       <c r="C69">
         <v>6592.8</v>
       </c>
       <c r="D69">
-        <v>2242.3</v>
+        <v>2242.3000000000002</v>
       </c>
       <c r="E69">
-        <v>2267.8</v>
+        <v>2267.8000000000002</v>
       </c>
       <c r="F69" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G69" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H69" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I69" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J69" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K69">
         <v>1684.11</v>
@@ -3345,9 +3361,9 @@
         <v>1684.89</v>
       </c>
     </row>
-    <row r="70" spans="1:12">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B70">
         <v>11613.9</v>
@@ -3362,19 +3378,19 @@
         <v>2581.48</v>
       </c>
       <c r="F70" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G70" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H70" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I70" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J70" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K70">
         <v>1850.74</v>
@@ -3383,9 +3399,9 @@
         <v>1793.47</v>
       </c>
     </row>
-    <row r="71" spans="1:12">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B71">
         <v>2580</v>
@@ -3400,19 +3416,19 @@
         <v>2324</v>
       </c>
       <c r="F71" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G71" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H71" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I71" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J71" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K71">
         <v>1707.35</v>
@@ -3421,15 +3437,15 @@
         <v>1725.68</v>
       </c>
     </row>
-    <row r="72" spans="1:12">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B72">
         <v>8061.2</v>
       </c>
       <c r="C72">
-        <v>4658.4</v>
+        <v>4658.3999999999996</v>
       </c>
       <c r="D72">
         <v>2510.56</v>
@@ -3438,19 +3454,19 @@
         <v>2475.9</v>
       </c>
       <c r="F72" t="s">
+        <v>110</v>
+      </c>
+      <c r="G72" t="s">
         <v>112</v>
       </c>
-      <c r="G72" t="s">
-        <v>114</v>
-      </c>
       <c r="H72" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I72" t="s">
+        <v>119</v>
+      </c>
+      <c r="J72" t="s">
         <v>121</v>
-      </c>
-      <c r="J72" t="s">
-        <v>123</v>
       </c>
       <c r="K72">
         <v>1846.26</v>
@@ -3459,9 +3475,9 @@
         <v>1855.21</v>
       </c>
     </row>
-    <row r="73" spans="1:12">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B73">
         <v>3605</v>
@@ -3470,25 +3486,25 @@
         <v>6281</v>
       </c>
       <c r="D73">
-        <v>2282.55</v>
+        <v>2282.5500000000002</v>
       </c>
       <c r="E73">
         <v>2295.56</v>
       </c>
       <c r="F73" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G73" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H73" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I73" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J73" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K73">
         <v>1749.52</v>
@@ -3497,9 +3513,9 @@
         <v>1690.34</v>
       </c>
     </row>
-    <row r="74" spans="1:12">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B74">
         <v>10488.9</v>
@@ -3508,25 +3524,25 @@
         <v>6352.3</v>
       </c>
       <c r="D74">
-        <v>2492.53</v>
+        <v>2492.5300000000002</v>
       </c>
       <c r="E74">
         <v>2471.06</v>
       </c>
       <c r="F74" t="s">
+        <v>111</v>
+      </c>
+      <c r="G74" t="s">
         <v>113</v>
       </c>
-      <c r="G74" t="s">
-        <v>115</v>
-      </c>
       <c r="H74" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I74" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J74" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K74">
         <v>1800.88</v>
@@ -3535,9 +3551,9 @@
         <v>1838.73</v>
       </c>
     </row>
-    <row r="75" spans="1:12">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B75">
         <v>7946.6</v>
@@ -3552,19 +3568,19 @@
         <v>2443.06</v>
       </c>
       <c r="F75" t="s">
+        <v>110</v>
+      </c>
+      <c r="G75" t="s">
         <v>112</v>
       </c>
-      <c r="G75" t="s">
-        <v>114</v>
-      </c>
       <c r="H75" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I75" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J75" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K75">
         <v>1853.08</v>
@@ -3573,36 +3589,36 @@
         <v>1821.71</v>
       </c>
     </row>
-    <row r="76" spans="1:12">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B76">
         <v>1579.4</v>
       </c>
       <c r="C76">
-        <v>618.7</v>
+        <v>618.70000000000005</v>
       </c>
       <c r="D76">
         <v>2402.75</v>
       </c>
       <c r="E76">
-        <v>2398.49</v>
+        <v>2398.4899999999998</v>
       </c>
       <c r="F76" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G76" t="s">
+        <v>114</v>
+      </c>
+      <c r="H76" t="s">
         <v>116</v>
       </c>
-      <c r="H76" t="s">
-        <v>118</v>
-      </c>
       <c r="I76" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J76" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K76">
         <v>1768.42</v>
@@ -3611,9 +3627,9 @@
         <v>1776.38</v>
       </c>
     </row>
-    <row r="77" spans="1:12">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B77">
         <v>10140.9</v>
@@ -3622,25 +3638,25 @@
         <v>4115.2</v>
       </c>
       <c r="D77">
-        <v>2545.32</v>
+        <v>2545.3200000000002</v>
       </c>
       <c r="E77">
-        <v>2505.8</v>
+        <v>2505.8000000000002</v>
       </c>
       <c r="F77" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G77" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H77" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I77" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J77" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K77">
         <v>1843.65</v>
@@ -3649,9 +3665,9 @@
         <v>1848.24</v>
       </c>
     </row>
-    <row r="78" spans="1:12">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B78">
         <v>11339.4</v>
@@ -3666,19 +3682,19 @@
         <v>2441.41</v>
       </c>
       <c r="F78" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G78" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H78" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I78" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J78" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K78">
         <v>1764.78</v>
@@ -3687,9 +3703,9 @@
         <v>1765.77</v>
       </c>
     </row>
-    <row r="79" spans="1:12">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B79">
         <v>10847</v>
@@ -3704,19 +3720,19 @@
         <v>2465.86</v>
       </c>
       <c r="F79" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G79" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H79" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I79" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J79" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K79">
         <v>1737.97</v>
@@ -3725,9 +3741,9 @@
         <v>1814.64</v>
       </c>
     </row>
-    <row r="80" spans="1:12">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B80">
         <v>6836.6</v>
@@ -3739,22 +3755,22 @@
         <v>2392.02</v>
       </c>
       <c r="E80">
-        <v>2376.97</v>
+        <v>2376.9699999999998</v>
       </c>
       <c r="F80" t="s">
+        <v>110</v>
+      </c>
+      <c r="G80" t="s">
         <v>112</v>
       </c>
-      <c r="G80" t="s">
-        <v>114</v>
-      </c>
       <c r="H80" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I80" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J80" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K80">
         <v>1793.28</v>
@@ -3763,9 +3779,9 @@
         <v>1820.88</v>
       </c>
     </row>
-    <row r="81" spans="1:12">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B81">
         <v>1745.5</v>
@@ -3780,19 +3796,19 @@
         <v>2413.11</v>
       </c>
       <c r="F81" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G81" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H81" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I81" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J81" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K81">
         <v>1751.37</v>
@@ -3801,9 +3817,9 @@
         <v>1781.91</v>
       </c>
     </row>
-    <row r="82" spans="1:12">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B82">
         <v>2309.6</v>
@@ -3818,19 +3834,19 @@
         <v>2302.09</v>
       </c>
       <c r="F82" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G82" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H82" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I82" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J82" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K82">
         <v>1734.13</v>
@@ -3839,9 +3855,9 @@
         <v>1684.61</v>
       </c>
     </row>
-    <row r="83" spans="1:12">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B83">
         <v>11134.9</v>
@@ -3850,25 +3866,25 @@
         <v>8020.4</v>
       </c>
       <c r="D83">
-        <v>2464.82</v>
+        <v>2464.8200000000002</v>
       </c>
       <c r="E83">
         <v>2412.46</v>
       </c>
       <c r="F83" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G83" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H83" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I83" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J83" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K83">
         <v>1813.23</v>
@@ -3877,9 +3893,9 @@
         <v>1838.37</v>
       </c>
     </row>
-    <row r="84" spans="1:12">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B84">
         <v>6627.9</v>
@@ -3894,19 +3910,19 @@
         <v>2234.92</v>
       </c>
       <c r="F84" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G84" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H84" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I84" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J84" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K84">
         <v>1748.8</v>
@@ -3915,9 +3931,9 @@
         <v>1638.31</v>
       </c>
     </row>
-    <row r="85" spans="1:12">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B85">
         <v>2166.6</v>
@@ -3932,19 +3948,19 @@
         <v>2267.14</v>
       </c>
       <c r="F85" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G85" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H85" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I85" t="s">
+        <v>119</v>
+      </c>
+      <c r="J85" t="s">
         <v>121</v>
-      </c>
-      <c r="J85" t="s">
-        <v>123</v>
       </c>
       <c r="K85">
         <v>1738.97</v>
@@ -3953,9 +3969,9 @@
         <v>1767.18</v>
       </c>
     </row>
-    <row r="86" spans="1:12">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B86">
         <v>10608.7</v>
@@ -3970,19 +3986,19 @@
         <v>2416.21</v>
       </c>
       <c r="F86" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G86" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H86" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I86" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J86" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K86">
         <v>1780.95</v>
@@ -3991,9 +4007,9 @@
         <v>1789.86</v>
       </c>
     </row>
-    <row r="87" spans="1:12">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B87">
         <v>7698.9</v>
@@ -4002,25 +4018,25 @@
         <v>466.5</v>
       </c>
       <c r="D87">
-        <v>2460.26</v>
+        <v>2460.2600000000002</v>
       </c>
       <c r="E87">
-        <v>2432.24</v>
+        <v>2432.2399999999998</v>
       </c>
       <c r="F87" t="s">
+        <v>110</v>
+      </c>
+      <c r="G87" t="s">
         <v>112</v>
       </c>
-      <c r="G87" t="s">
-        <v>114</v>
-      </c>
       <c r="H87" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I87" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J87" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K87">
         <v>1721.86</v>
@@ -4029,15 +4045,15 @@
         <v>1817.6</v>
       </c>
     </row>
-    <row r="88" spans="1:12">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B88">
         <v>6836.3</v>
       </c>
       <c r="C88">
-        <v>302.9</v>
+        <v>302.89999999999998</v>
       </c>
       <c r="D88">
         <v>2459.34</v>
@@ -4046,19 +4062,19 @@
         <v>2534.11</v>
       </c>
       <c r="F88" t="s">
+        <v>110</v>
+      </c>
+      <c r="G88" t="s">
         <v>112</v>
       </c>
-      <c r="G88" t="s">
-        <v>114</v>
-      </c>
       <c r="H88" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I88" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J88" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K88">
         <v>1762.36</v>
@@ -4067,9 +4083,9 @@
         <v>1860.8</v>
       </c>
     </row>
-    <row r="89" spans="1:12">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B89">
         <v>4515.5</v>
@@ -4078,25 +4094,25 @@
         <v>202.2</v>
       </c>
       <c r="D89">
-        <v>2484.7</v>
+        <v>2484.6999999999998</v>
       </c>
       <c r="E89">
         <v>2498.98</v>
       </c>
       <c r="F89" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G89" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H89" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I89" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J89" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K89">
         <v>1848.32</v>
@@ -4105,36 +4121,36 @@
         <v>1830.38</v>
       </c>
     </row>
-    <row r="90" spans="1:12">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B90">
         <v>4931.5</v>
       </c>
       <c r="C90">
-        <v>2527.7</v>
+        <v>2527.6999999999998</v>
       </c>
       <c r="D90">
-        <v>2418.2</v>
+        <v>2418.1999999999998</v>
       </c>
       <c r="E90">
         <v>2328.66</v>
       </c>
       <c r="F90" t="s">
+        <v>110</v>
+      </c>
+      <c r="G90" t="s">
         <v>112</v>
       </c>
-      <c r="G90" t="s">
-        <v>114</v>
-      </c>
       <c r="H90" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I90" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J90" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K90">
         <v>1840.97</v>
@@ -4143,15 +4159,15 @@
         <v>1779.43</v>
       </c>
     </row>
-    <row r="91" spans="1:12">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B91">
         <v>2873.9</v>
       </c>
       <c r="C91">
-        <v>2485.7</v>
+        <v>2485.6999999999998</v>
       </c>
       <c r="D91">
         <v>2372.36</v>
@@ -4160,19 +4176,19 @@
         <v>2355.1</v>
       </c>
       <c r="F91" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G91" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H91" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I91" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J91" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K91">
         <v>1760.5</v>
@@ -4181,9 +4197,9 @@
         <v>1751.01</v>
       </c>
     </row>
-    <row r="92" spans="1:12">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B92">
         <v>456.7</v>
@@ -4195,22 +4211,22 @@
         <v>2344.11</v>
       </c>
       <c r="E92">
-        <v>2363.93</v>
+        <v>2363.9299999999998</v>
       </c>
       <c r="F92" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G92" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H92" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I92" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J92" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K92">
         <v>1729.12</v>
@@ -4219,9 +4235,9 @@
         <v>1728.42</v>
       </c>
     </row>
-    <row r="93" spans="1:12">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B93">
         <v>10514.6</v>
@@ -4233,22 +4249,22 @@
         <v>2506.34</v>
       </c>
       <c r="E93">
-        <v>2515.76</v>
+        <v>2515.7600000000002</v>
       </c>
       <c r="F93" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G93" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H93" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I93" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J93" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K93">
         <v>1796.09</v>
@@ -4257,9 +4273,9 @@
         <v>1839.96</v>
       </c>
     </row>
-    <row r="94" spans="1:12">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B94">
         <v>5612.8</v>
@@ -4274,19 +4290,19 @@
         <v>2324.52</v>
       </c>
       <c r="F94" t="s">
+        <v>110</v>
+      </c>
+      <c r="G94" t="s">
         <v>112</v>
       </c>
-      <c r="G94" t="s">
-        <v>114</v>
-      </c>
       <c r="H94" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I94" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J94" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K94">
         <v>1825.98</v>
@@ -4295,9 +4311,9 @@
         <v>1673.04</v>
       </c>
     </row>
-    <row r="95" spans="1:12">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B95">
         <v>6571.6</v>
@@ -4306,25 +4322,25 @@
         <v>5903.9</v>
       </c>
       <c r="D95">
-        <v>2408.28</v>
+        <v>2408.2800000000002</v>
       </c>
       <c r="E95">
         <v>2505.87</v>
       </c>
       <c r="F95" t="s">
+        <v>110</v>
+      </c>
+      <c r="G95" t="s">
         <v>112</v>
       </c>
-      <c r="G95" t="s">
-        <v>114</v>
-      </c>
       <c r="H95" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I95" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J95" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K95">
         <v>1733.92</v>
@@ -4333,9 +4349,9 @@
         <v>1827.92</v>
       </c>
     </row>
-    <row r="96" spans="1:12">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B96">
         <v>3866</v>
@@ -4350,19 +4366,19 @@
         <v>2457.13</v>
       </c>
       <c r="F96" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G96" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H96" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I96" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J96" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K96">
         <v>1765.93</v>
@@ -4371,9 +4387,9 @@
         <v>1742.5</v>
       </c>
     </row>
-    <row r="97" spans="1:12">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B97">
         <v>9015.9</v>
@@ -4388,19 +4404,19 @@
         <v>2502.39</v>
       </c>
       <c r="F97" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G97" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H97" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I97" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J97" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K97">
         <v>1817.56</v>
@@ -4409,12 +4425,12 @@
         <v>1832.29</v>
       </c>
     </row>
-    <row r="98" spans="1:12">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B98">
-        <v>302.4</v>
+        <v>302.39999999999998</v>
       </c>
       <c r="C98">
         <v>210.8</v>
@@ -4426,19 +4442,19 @@
         <v>2361.27</v>
       </c>
       <c r="F98" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G98" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H98" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I98" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J98" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K98">
         <v>1762.85</v>
@@ -4447,9 +4463,9 @@
         <v>1784.06</v>
       </c>
     </row>
-    <row r="99" spans="1:12">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B99">
         <v>4466.2</v>
@@ -4461,22 +4477,22 @@
         <v>2389.04</v>
       </c>
       <c r="E99">
-        <v>2366.32</v>
+        <v>2366.3200000000002</v>
       </c>
       <c r="F99" t="s">
+        <v>110</v>
+      </c>
+      <c r="G99" t="s">
         <v>112</v>
       </c>
-      <c r="G99" t="s">
-        <v>114</v>
-      </c>
       <c r="H99" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I99" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J99" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K99">
         <v>1765.02</v>
@@ -4485,9 +4501,9 @@
         <v>1783.7</v>
       </c>
     </row>
-    <row r="100" spans="1:12">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B100">
         <v>364.2</v>
@@ -4502,19 +4518,19 @@
         <v>2193.88</v>
       </c>
       <c r="F100" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G100" t="s">
+        <v>114</v>
+      </c>
+      <c r="H100" t="s">
         <v>116</v>
       </c>
-      <c r="H100" t="s">
-        <v>118</v>
-      </c>
       <c r="I100" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J100" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K100">
         <v>1707.02</v>
@@ -4523,9 +4539,9 @@
         <v>1660.74</v>
       </c>
     </row>
-    <row r="101" spans="1:12">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B101">
         <v>1474.7</v>
@@ -4540,19 +4556,19 @@
         <v>2312.87</v>
       </c>
       <c r="F101" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G101" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H101" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I101" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J101" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K101">
         <v>1667.11</v>
